--- a/output/pdf_financials_xlsx/TSL.xlsx
+++ b/output/pdf_financials_xlsx/TSL.xlsx
@@ -4263,19 +4263,19 @@
         <v>0.000238</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.027333</v>
+        <v>5.5e-05</v>
       </c>
       <c r="L75" s="3" t="n">
         <v>1.9e-05</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.01511</v>
+        <v>3e-05</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.018802</v>
+        <v>0.002213</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.018802</v>
+        <v>0.003012</v>
       </c>
     </row>
     <row r="76">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -21546,7 +21546,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">

--- a/output/pdf_financials_xlsx/TSL.xlsx
+++ b/output/pdf_financials_xlsx/TSL.xlsx
@@ -1002,17 +1002,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000763</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>0.000452</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>0.000181</v>
       </c>
     </row>
     <row r="13">
@@ -1903,7 +1899,7 @@
         <v>0.044211</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.011507</v>
+        <v>0.010744</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2005,7 +2001,7 @@
         <v>0.044211</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.011507</v>
+        <v>0.010744</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2058,7 +2054,7 @@
         <v>13.27908883662675</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>4.905948361131007</v>
+        <v>4.580647361779051</v>
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
@@ -2191,46 +2187,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>3.852</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.371</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001264</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.002309</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001326</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.001351</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.001651</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.001277</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.000907</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.033251</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.033251</v>
+        <v>0.014976</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.007551</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.008697</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.008697</v>
       </c>
     </row>
     <row r="35">
@@ -2289,46 +2285,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>3.852</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.371</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001264</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.002309</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.001326</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.001351</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.001651</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.001277</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.000907</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.033251</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.033251</v>
+        <v>0.014976</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.007551</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.008697</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.008697</v>
       </c>
     </row>
     <row r="37">
@@ -2877,31 +2873,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>6.385</v>
+        <v>2.533</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.571</v>
+        <v>2.2</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.002955</v>
+        <v>0.001691</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.006223</v>
+        <v>0.003914</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.005202</v>
+        <v>0.003876</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.005582</v>
+        <v>0.004231</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.00522</v>
+        <v>0.003569</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.004035</v>
+        <v>0.002758</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.004666</v>
+        <v>0.003759</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.006785</v>
@@ -2910,13 +2906,13 @@
         <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.027209</v>
+        <v>0.019658</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.020565</v>
+        <v>0.011868</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.000543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -11436,7 +11432,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -14286,7 +14282,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -19446,7 +19442,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -30248,7 +30244,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E271" s="5" t="n">
@@ -57950,7 +57946,7 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
@@ -61664,7 +61660,7 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">

--- a/output/pdf_financials_xlsx/TSL.xlsx
+++ b/output/pdf_financials_xlsx/TSL.xlsx
@@ -6063,16 +6063,16 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>2.4e-05</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>3e-06</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.069244</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
@@ -40970,7 +40970,11 @@
           <t>Proceeds on disposal of property plant and equipment - 69,244</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
           <t>-</t>
@@ -52410,7 +52414,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr">
         <is>
           <t>-</t>
@@ -54340,7 +54348,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E557" s="5" t="n">
         <v>0.049</v>
       </c>

--- a/output/pdf_financials_xlsx/TSL.xlsx
+++ b/output/pdf_financials_xlsx/TSL.xlsx
@@ -1185,7 +1185,7 @@
         <v>0.001409</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.016147</v>
+        <v>0.020533</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0.015001</v>
@@ -1232,13 +1232,13 @@
         <v>0.458</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>9.500000000000001e-05</v>
+        <v>-9.500000000000001e-05</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.000431</v>
+        <v>0.000431</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.004386</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0.000504</v>
@@ -1250,7 +1250,7 @@
         <v>0.000332</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3.1e-05</v>
+        <v>1.4e-05</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0.025507</v>
@@ -1878,7 +1878,7 @@
         <v>0.001409</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.016147</v>
+        <v>0.020533</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>0.015001</v>
@@ -1980,7 +1980,7 @@
         <v>0.004231</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.019262</v>
+        <v>0.023648</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.01832</v>
@@ -2033,7 +2033,7 @@
         <v>2.300156569390684</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>8.328937241098993</v>
+        <v>10.22545467124437</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>7.922059389499812</v>
@@ -2086,7 +2086,7 @@
         <v>30.58907026259759</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>21.36073637559051</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>3.359776014932338</v>
@@ -2098,7 +2098,7 @@
         <v>6.970396808733992</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0.5937559854434017</v>
+        <v>-0.2681478643937943</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>22.47748462257001</v>
@@ -5428,7 +5428,7 @@
         <v>10.371</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>-0.655</v>
+        <v>-0.000653</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>0.0009779999999999999</v>
@@ -6516,28 +6516,28 @@
         <v>0</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-0.000107</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-0.000145</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-0.004446</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-0.001262</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-0.000721</v>
       </c>
       <c r="K121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-0.000534</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-0.003653</v>
       </c>
       <c r="N121" s="3" t="n">
         <v>0</v>
@@ -33132,7 +33132,11 @@
           <t>Deferred income tax expense (recovery) (501) 1,101</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -35512,7 +35516,11 @@
           <t>Deferred income tax expense 224 1,795</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -37786,7 +37794,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -39184,7 +39196,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -40206,7 +40222,11 @@
           <t>Deferred income tax expense (recovery) 6 -</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -42342,7 +42362,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -42722,7 +42746,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -43642,7 +43670,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
           <t>-</t>
@@ -44318,7 +44350,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E438" t="inlineStr">
         <is>
           <t>-</t>
@@ -45254,7 +45290,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>
@@ -48712,7 +48752,11 @@
           <t>Repurchase of common shares (78) (77)</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr">
         <is>
           <t>-</t>
@@ -54004,7 +54048,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E553" t="inlineStr">
         <is>
           <t>-</t>
@@ -55732,7 +55780,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D573" t="inlineStr"/>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E573" s="5" t="n">
         <v>-0.013</v>
       </c>
@@ -69590,7 +69642,11 @@
           <t>Current income tax recovery (expense) (Note 15)</t>
         </is>
       </c>
-      <c r="D737" t="inlineStr"/>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E737" t="inlineStr">
         <is>
           <t>-</t>
@@ -69670,7 +69726,11 @@
           <t>Deferred income tax recovery (expense) (Note 15)</t>
         </is>
       </c>
-      <c r="D738" t="inlineStr"/>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E738" t="inlineStr">
         <is>
           <t>-</t>
@@ -74000,7 +74060,11 @@
           <t>Income tax recovery (expense) (Note 14) 329 5,360</t>
         </is>
       </c>
-      <c r="D791" t="inlineStr"/>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E791" t="inlineStr">
         <is>
           <t>-</t>
@@ -75892,7 +75956,11 @@
           <t>Income tax recovery (expense) (Note 17) 5,360 245</t>
         </is>
       </c>
-      <c r="D814" t="inlineStr"/>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E814" t="inlineStr">
         <is>
           <t>-</t>
@@ -77644,7 +77712,11 @@
           <t>Income tax recovery (expense) (Note 16)</t>
         </is>
       </c>
-      <c r="D835" t="inlineStr"/>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E835" t="inlineStr">
         <is>
           <t>-</t>
@@ -78652,7 +78724,11 @@
           <t>Income tax recovery (expense) (Note 18)</t>
         </is>
       </c>
-      <c r="D847" t="inlineStr"/>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E847" t="inlineStr">
         <is>
           <t>-</t>
